--- a/Employee_Reports_wi48/Ray Maitem Maureal Q0477.xlsx
+++ b/Employee_Reports_wi48/Ray Maitem Maureal Q0477.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-252</v>
+        <v>-255</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1815,9 +1815,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>10-Apr-2025</t>
@@ -1829,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-94</v>
+        <v>-97</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1844,53 +1856,53 @@
       <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-041</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1927,11 +1939,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1976,11 +1988,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2025,11 +2037,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2074,11 +2086,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2111,11 +2123,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2160,11 +2172,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2209,11 +2221,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2246,11 +2258,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2283,11 +2295,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2320,11 +2332,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2357,11 +2369,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2406,11 +2418,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2443,11 +2455,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3055,7 +3067,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3096,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3113,7 +3125,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3142,7 +3154,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3171,7 +3183,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3194,7 +3206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3252,21 +3264,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ews 20ft</t>
+          <t>stacker crane</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3281,21 +3293,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ews 10 ft</t>
+          <t>h9tv</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3310,21 +3322,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>ews 20ft</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7957</v>
+        <v>7948</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3339,21 +3351,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>truckdock 15ft</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>30-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>24-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3368,21 +3380,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>truckdock  20ft</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7955</v>
+        <v>7954</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3397,7 +3409,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>turntable</t>
+          <t>truckdock 15ft</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3411,7 +3423,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3426,21 +3438,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>truckdock  20ft</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7957</v>
+        <v>7952</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3455,21 +3467,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>uldtv 20ft</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>30-May-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>24-Apr-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7958</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3484,21 +3496,21 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>uldtv 15ft</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7958</v>
+        <v>7954</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3513,21 +3525,21 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>bbtv 20ft</t>
+          <t>uldtv 20ft</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3542,21 +3554,21 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bbtv 15ft</t>
+          <t>uldtv 15ft</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3571,21 +3583,21 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>bbtv 20ft</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7950</v>
+        <v>7966</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3600,21 +3612,21 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>bbtv 15ft</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7952</v>
+        <v>7966</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3629,21 +3641,21 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>fmc deck</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>24-May-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>18-Apr-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3658,21 +3670,21 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>cs placing deck</t>
+          <t>powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>16-May-2048</t>
+          <t>20-Apr-2048</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7978</v>
+        <v>7949</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3687,21 +3699,21 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>cs input and output conveyor</t>
+          <t>non powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16-May-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7978</v>
+        <v>7952</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3716,21 +3728,21 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ball deck</t>
+          <t>cs placing deck</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>21-Jun-2026</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>16-May-2048</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7950</v>
+        <v>7975</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3745,28 +3757,86 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>cs input and output conveyor</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>21-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>16-May-2048</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7975</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>24-May-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>18-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7947</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>floor scale</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>26-May-2026</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>20-Apr-2048</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>7952</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
+        <v>7949</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
